--- a/新数据生成/#关卡设计表_1导.xlsx
+++ b/新数据生成/#关卡设计表_1导.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="19">
   <si>
     <t>##var</t>
   </si>
@@ -53,6 +53,30 @@
   <si>
     <t/>
   </si>
+  <si>
+    <t>简单</t>
+  </si>
+  <si>
+    <t>森林</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>草原</t>
+  </si>
+  <si>
+    <t>困难</t>
+  </si>
+  <si>
+    <t>雪山</t>
+  </si>
+  <si>
+    <t>很难</t>
+  </si>
+  <si>
+    <t>极难</t>
+  </si>
 </sst>
 </file>
 
@@ -67,26 +91,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -102,7 +124,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -119,20 +148,20 @@
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -502,13 +531,13 @@
         <v>10010</v>
       </c>
       <c r="C4" s="2">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
@@ -519,10 +548,10 @@
         <v>3.2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
@@ -530,13 +559,13 @@
         <v>10030</v>
       </c>
       <c r="C6" s="2">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
@@ -544,13 +573,13 @@
         <v>10040</v>
       </c>
       <c r="C7" s="2">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
@@ -558,13 +587,13 @@
         <v>10050</v>
       </c>
       <c r="C8" s="2">
-        <v>3.7</v>
+        <v>3.6934999999999998</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
@@ -572,13 +601,13 @@
         <v>10060</v>
       </c>
       <c r="C9" s="2">
-        <v>3.9</v>
+        <v>3.8689</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
@@ -586,13 +615,13 @@
         <v>10070</v>
       </c>
       <c r="C10" s="2">
-        <v>4</v>
+        <v>4.0492999999999997</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
@@ -600,13 +629,13 @@
         <v>10080</v>
       </c>
       <c r="C11" s="2">
-        <v>4.2</v>
+        <v>4.2213000000000003</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
@@ -614,13 +643,13 @@
         <v>10090</v>
       </c>
       <c r="C12" s="2">
-        <v>4.4000000000000004</v>
+        <v>4.3935000000000004</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
@@ -628,13 +657,13 @@
         <v>10100</v>
       </c>
       <c r="C13" s="2">
-        <v>4.5999999999999996</v>
+        <v>4.5682999999999998</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
@@ -642,7 +671,7 @@
         <v>10110</v>
       </c>
       <c r="C14" s="2">
-        <v>4.7</v>
+        <v>4.7430000000000003</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>10</v>
@@ -656,7 +685,7 @@
         <v>10120</v>
       </c>
       <c r="C15" s="2">
-        <v>4.9000000000000004</v>
+        <v>4.9172000000000002</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -670,7 +699,7 @@
         <v>10130</v>
       </c>
       <c r="C16" s="2">
-        <v>5.0999999999999996</v>
+        <v>5.0919999999999996</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -684,7 +713,7 @@
         <v>10140</v>
       </c>
       <c r="C17" s="2">
-        <v>5.3</v>
+        <v>5.2670000000000003</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>10</v>
@@ -698,7 +727,7 @@
         <v>10150</v>
       </c>
       <c r="C18" s="2">
-        <v>5.4</v>
+        <v>5.4408000000000003</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>10</v>
@@ -712,7 +741,7 @@
         <v>10160</v>
       </c>
       <c r="C19" s="2">
-        <v>5.6</v>
+        <v>5.6146000000000003</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -726,7 +755,7 @@
         <v>10170</v>
       </c>
       <c r="C20" s="2">
-        <v>5.8</v>
+        <v>5.7888000000000002</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -740,7 +769,7 @@
         <v>10180</v>
       </c>
       <c r="C21" s="2">
-        <v>6</v>
+        <v>5.9637000000000002</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -754,7 +783,7 @@
         <v>10190</v>
       </c>
       <c r="C22" s="2">
-        <v>6.1</v>
+        <v>6.1379000000000001</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -768,7 +797,7 @@
         <v>10200</v>
       </c>
       <c r="C23" s="2">
-        <v>6.3</v>
+        <v>6.3125999999999998</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>10</v>
@@ -782,7 +811,7 @@
         <v>10210</v>
       </c>
       <c r="C24" s="2">
-        <v>6.5</v>
+        <v>6.4863999999999997</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>10</v>
@@ -796,7 +825,7 @@
         <v>10220</v>
       </c>
       <c r="C25" s="2">
-        <v>6.7</v>
+        <v>6.6604999999999999</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>10</v>
@@ -810,7 +839,7 @@
         <v>10230</v>
       </c>
       <c r="C26" s="2">
-        <v>6.8</v>
+        <v>6.8349000000000002</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>10</v>
@@ -824,7 +853,7 @@
         <v>10240</v>
       </c>
       <c r="C27" s="2">
-        <v>7</v>
+        <v>7.0083000000000002</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>10</v>
@@ -838,7 +867,7 @@
         <v>10250</v>
       </c>
       <c r="C28" s="2">
-        <v>7.2</v>
+        <v>7.1832000000000003</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
@@ -852,7 +881,7 @@
         <v>10260</v>
       </c>
       <c r="C29" s="2">
-        <v>7.4</v>
+        <v>7.3582999999999998</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
@@ -866,7 +895,7 @@
         <v>10270</v>
       </c>
       <c r="C30" s="2">
-        <v>7.5</v>
+        <v>7.5328999999999997</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -880,7 +909,7 @@
         <v>10280</v>
       </c>
       <c r="C31" s="2">
-        <v>7.7</v>
+        <v>7.7065999999999999</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>10</v>
@@ -894,7 +923,7 @@
         <v>10290</v>
       </c>
       <c r="C32" s="2">
-        <v>7.9</v>
+        <v>7.8804999999999996</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>10</v>
@@ -908,7 +937,7 @@
         <v>10300</v>
       </c>
       <c r="C33" s="2">
-        <v>8.1</v>
+        <v>8.0551999999999992</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>10</v>
@@ -922,7 +951,7 @@
         <v>10310</v>
       </c>
       <c r="C34" s="2">
-        <v>8.1999999999999993</v>
+        <v>8.2296999999999993</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>10</v>
@@ -936,7 +965,7 @@
         <v>10320</v>
       </c>
       <c r="C35" s="2">
-        <v>8.4</v>
+        <v>8.4039000000000001</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>10</v>
@@ -950,7 +979,7 @@
         <v>10330</v>
       </c>
       <c r="C36" s="2">
-        <v>8.6</v>
+        <v>8.5782000000000007</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>10</v>
@@ -964,7 +993,7 @@
         <v>10340</v>
       </c>
       <c r="C37" s="2">
-        <v>8.8000000000000007</v>
+        <v>8.7528000000000006</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>10</v>
@@ -978,7 +1007,7 @@
         <v>10350</v>
       </c>
       <c r="C38" s="2">
-        <v>8.9</v>
+        <v>8.9265000000000008</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>10</v>
@@ -992,7 +1021,7 @@
         <v>10360</v>
       </c>
       <c r="C39" s="2">
-        <v>9.1</v>
+        <v>9.1013000000000002</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
@@ -1006,7 +1035,7 @@
         <v>10370</v>
       </c>
       <c r="C40" s="2">
-        <v>9.3000000000000007</v>
+        <v>9.2753999999999994</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
@@ -1020,7 +1049,7 @@
         <v>10380</v>
       </c>
       <c r="C41" s="2">
-        <v>9.4</v>
+        <v>9.4495000000000005</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
@@ -1034,7 +1063,7 @@
         <v>10390</v>
       </c>
       <c r="C42" s="2">
-        <v>9.6</v>
+        <v>9.6242000000000001</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
@@ -1048,7 +1077,7 @@
         <v>10400</v>
       </c>
       <c r="C43" s="2">
-        <v>9.8000000000000007</v>
+        <v>9.7982999999999993</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
@@ -1062,7 +1091,7 @@
         <v>10410</v>
       </c>
       <c r="C44" s="2">
-        <v>10</v>
+        <v>9.9724000000000004</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>10</v>
@@ -1076,7 +1105,7 @@
         <v>10420</v>
       </c>
       <c r="C45" s="2">
-        <v>10.1</v>
+        <v>10.1469</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>10</v>
@@ -1090,7 +1119,7 @@
         <v>10430</v>
       </c>
       <c r="C46" s="2">
-        <v>10.3</v>
+        <v>10.321099999999999</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>10</v>
@@ -1104,7 +1133,7 @@
         <v>10440</v>
       </c>
       <c r="C47" s="2">
-        <v>10.5</v>
+        <v>10.495900000000001</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>10</v>
@@ -1118,7 +1147,7 @@
         <v>10450</v>
       </c>
       <c r="C48" s="2">
-        <v>10.7</v>
+        <v>10.669499999999999</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>10</v>
@@ -1132,7 +1161,7 @@
         <v>10460</v>
       </c>
       <c r="C49" s="2">
-        <v>10.8</v>
+        <v>10.844200000000001</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>10</v>
@@ -1146,7 +1175,7 @@
         <v>10470</v>
       </c>
       <c r="C50" s="2">
-        <v>11</v>
+        <v>11.0185</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>10</v>
@@ -1160,7 +1189,7 @@
         <v>10480</v>
       </c>
       <c r="C51" s="2">
-        <v>11.2</v>
+        <v>11.1927</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>10</v>
@@ -1174,7 +1203,7 @@
         <v>10490</v>
       </c>
       <c r="C52" s="2">
-        <v>11.4</v>
+        <v>11.367599999999999</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>10</v>
@@ -1188,7 +1217,7 @@
         <v>10500</v>
       </c>
       <c r="C53" s="2">
-        <v>11.5</v>
+        <v>11.541600000000001</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>10</v>
@@ -1202,7 +1231,7 @@
         <v>10510</v>
       </c>
       <c r="C54" s="2">
-        <v>11.7</v>
+        <v>11.7158</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>10</v>
@@ -1216,7 +1245,7 @@
         <v>10520</v>
       </c>
       <c r="C55" s="2">
-        <v>11.9</v>
+        <v>11.889799999999999</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>10</v>
@@ -1230,7 +1259,7 @@
         <v>10530</v>
       </c>
       <c r="C56" s="2">
-        <v>12.1</v>
+        <v>12.064500000000001</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>10</v>
@@ -1244,7 +1273,7 @@
         <v>10540</v>
       </c>
       <c r="C57" s="2">
-        <v>12.2</v>
+        <v>12.238799999999999</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>10</v>
@@ -1258,7 +1287,7 @@
         <v>10550</v>
       </c>
       <c r="C58" s="2">
-        <v>12.4</v>
+        <v>12.4129</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>10</v>
@@ -1272,7 +1301,7 @@
         <v>10560</v>
       </c>
       <c r="C59" s="2">
-        <v>12.6</v>
+        <v>12.5871</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>10</v>
@@ -1286,7 +1315,7 @@
         <v>10570</v>
       </c>
       <c r="C60" s="2">
-        <v>12.8</v>
+        <v>12.760999999999999</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>10</v>
@@ -1300,7 +1329,7 @@
         <v>10580</v>
       </c>
       <c r="C61" s="2">
-        <v>12.9</v>
+        <v>12.935700000000001</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>10</v>
@@ -1314,7 +1343,7 @@
         <v>10590</v>
       </c>
       <c r="C62" s="2">
-        <v>13.1</v>
+        <v>13.110200000000001</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>10</v>
@@ -1328,7 +1357,7 @@
         <v>10600</v>
       </c>
       <c r="C63" s="2">
-        <v>13.3</v>
+        <v>13.2845</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>10</v>
@@ -1342,7 +1371,7 @@
         <v>10610</v>
       </c>
       <c r="C64" s="2">
-        <v>13.5</v>
+        <v>13.458399999999999</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>10</v>
@@ -1356,7 +1385,7 @@
         <v>10620</v>
       </c>
       <c r="C65" s="2">
-        <v>13.6</v>
+        <v>13.6328</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>10</v>
@@ -1370,7 +1399,7 @@
         <v>10630</v>
       </c>
       <c r="C66" s="2">
-        <v>13.8</v>
+        <v>13.807499999999999</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>10</v>
@@ -1384,7 +1413,7 @@
         <v>10640</v>
       </c>
       <c r="C67" s="2">
-        <v>14</v>
+        <v>13.981999999999999</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>10</v>
@@ -1398,7 +1427,7 @@
         <v>10650</v>
       </c>
       <c r="C68" s="2">
-        <v>14.2</v>
+        <v>14.156700000000001</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>10</v>
@@ -1412,7 +1441,7 @@
         <v>10660</v>
       </c>
       <c r="C69" s="2">
-        <v>14.3</v>
+        <v>14.3307</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>10</v>
@@ -1426,7 +1455,7 @@
         <v>10670</v>
       </c>
       <c r="C70" s="2">
-        <v>14.5</v>
+        <v>14.505100000000001</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>10</v>
@@ -1440,7 +1469,7 @@
         <v>10680</v>
       </c>
       <c r="C71" s="2">
-        <v>14.7</v>
+        <v>14.6793</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>10</v>
@@ -1454,7 +1483,7 @@
         <v>10690</v>
       </c>
       <c r="C72" s="2">
-        <v>14.9</v>
+        <v>14.853300000000001</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>10</v>
@@ -1468,7 +1497,7 @@
         <v>10700</v>
       </c>
       <c r="C73" s="2">
-        <v>15</v>
+        <v>15.027900000000001</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>10</v>
@@ -1482,7 +1511,7 @@
         <v>10710</v>
       </c>
       <c r="C74" s="2">
-        <v>15.2</v>
+        <v>15.202400000000001</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>10</v>
@@ -1496,7 +1525,7 @@
         <v>10720</v>
       </c>
       <c r="C75" s="2">
-        <v>15.4</v>
+        <v>15.3766</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>10</v>
@@ -1510,7 +1539,7 @@
         <v>10730</v>
       </c>
       <c r="C76" s="2">
-        <v>15.6</v>
+        <v>15.5504</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>10</v>
@@ -1524,7 +1553,7 @@
         <v>10740</v>
       </c>
       <c r="C77" s="2">
-        <v>15.7</v>
+        <v>15.725</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>10</v>
@@ -1538,7 +1567,7 @@
         <v>10750</v>
       </c>
       <c r="C78" s="2">
-        <v>15.9</v>
+        <v>15.8992</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>10</v>
@@ -1552,7 +1581,7 @@
         <v>10760</v>
       </c>
       <c r="C79" s="2">
-        <v>16.100000000000001</v>
+        <v>16.0731</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>10</v>
@@ -1566,7 +1595,7 @@
         <v>10770</v>
       </c>
       <c r="C80" s="2">
-        <v>16.2</v>
+        <v>16.247599999999998</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>10</v>
@@ -1580,7 +1609,7 @@
         <v>10780</v>
       </c>
       <c r="C81" s="2">
-        <v>16.399999999999999</v>
+        <v>16.4224</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>10</v>
@@ -1594,7 +1623,7 @@
         <v>10790</v>
       </c>
       <c r="C82" s="2">
-        <v>16.600000000000001</v>
+        <v>16.597000000000001</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>10</v>
@@ -1608,7 +1637,7 @@
         <v>10800</v>
       </c>
       <c r="C83" s="2">
-        <v>16.8</v>
+        <v>16.7715</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>10</v>
@@ -1622,7 +1651,7 @@
         <v>10810</v>
       </c>
       <c r="C84" s="2">
-        <v>16.899999999999999</v>
+        <v>16.945799999999998</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>10</v>
@@ -1636,7 +1665,7 @@
         <v>10820</v>
       </c>
       <c r="C85" s="2">
-        <v>17.100000000000001</v>
+        <v>17.119700000000002</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>10</v>
@@ -1650,7 +1679,7 @@
         <v>10830</v>
       </c>
       <c r="C86" s="2">
-        <v>17.3</v>
+        <v>17.294</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>10</v>
@@ -1664,7 +1693,7 @@
         <v>10840</v>
       </c>
       <c r="C87" s="2">
-        <v>17.5</v>
+        <v>17.468499999999999</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>10</v>
@@ -1678,7 +1707,7 @@
         <v>10850</v>
       </c>
       <c r="C88" s="2">
-        <v>17.600000000000001</v>
+        <v>17.6434</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>10</v>
@@ -1692,7 +1721,7 @@
         <v>10860</v>
       </c>
       <c r="C89" s="2">
-        <v>17.8</v>
+        <v>17.8172</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>10</v>
@@ -1706,7 +1735,7 @@
         <v>10870</v>
       </c>
       <c r="C90" s="2">
-        <v>18</v>
+        <v>17.991499999999998</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>10</v>
@@ -1720,7 +1749,7 @@
         <v>10880</v>
       </c>
       <c r="C91" s="2">
-        <v>18.2</v>
+        <v>18.165199999999999</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>10</v>
@@ -1734,7 +1763,7 @@
         <v>10890</v>
       </c>
       <c r="C92" s="2">
-        <v>18.3</v>
+        <v>18.339400000000001</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>10</v>
@@ -1748,7 +1777,7 @@
         <v>10900</v>
       </c>
       <c r="C93" s="2">
-        <v>18.5</v>
+        <v>18.513400000000001</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>10</v>
@@ -1762,7 +1791,7 @@
         <v>10910</v>
       </c>
       <c r="C94" s="2">
-        <v>18.7</v>
+        <v>18.688700000000001</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>10</v>
@@ -1776,7 +1805,7 @@
         <v>10920</v>
       </c>
       <c r="C95" s="2">
-        <v>18.899999999999999</v>
+        <v>18.863099999999999</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>10</v>
@@ -1790,7 +1819,7 @@
         <v>10930</v>
       </c>
       <c r="C96" s="2">
-        <v>19</v>
+        <v>19.036899999999999</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>10</v>
@@ -1804,7 +1833,7 @@
         <v>10940</v>
       </c>
       <c r="C97" s="2">
-        <v>19.2</v>
+        <v>19.210699999999999</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>10</v>
@@ -1818,7 +1847,7 @@
         <v>10950</v>
       </c>
       <c r="C98" s="2">
-        <v>19.399999999999999</v>
+        <v>19.385200000000001</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>10</v>
@@ -1832,7 +1861,7 @@
         <v>10960</v>
       </c>
       <c r="C99" s="2">
-        <v>19.600000000000001</v>
+        <v>19.559899999999999</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>10</v>
@@ -1846,7 +1875,7 @@
         <v>10970</v>
       </c>
       <c r="C100" s="2">
-        <v>19.7</v>
+        <v>19.733699999999999</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>10</v>
@@ -1860,7 +1889,7 @@
         <v>10980</v>
       </c>
       <c r="C101" s="2">
-        <v>19.899999999999999</v>
+        <v>19.907800000000002</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>10</v>
@@ -1874,7 +1903,7 @@
         <v>10990</v>
       </c>
       <c r="C102" s="2">
-        <v>20.100000000000001</v>
+        <v>20.0822</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>10</v>
@@ -1888,7 +1917,7 @@
         <v>11000</v>
       </c>
       <c r="C103" s="2">
-        <v>20.2</v>
+        <v>20.198699999999999</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>10</v>
@@ -1898,7 +1927,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/新数据生成/#关卡设计表_1导.xlsx
+++ b/新数据生成/#关卡设计表_1导.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="14">
   <si>
     <t>##var</t>
   </si>
@@ -28,6 +28,15 @@
   </si>
   <si>
     <t>阵容强度</t>
+  </si>
+  <si>
+    <t>绿色等级</t>
+  </si>
+  <si>
+    <t>蓝色等级</t>
+  </si>
+  <si>
+    <t>紫色等级</t>
   </si>
   <si>
     <t>关卡难度</t>
@@ -52,30 +61,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>简单</t>
-  </si>
-  <si>
-    <t>森林</t>
-  </si>
-  <si>
-    <t>普通</t>
-  </si>
-  <si>
-    <t>草原</t>
-  </si>
-  <si>
-    <t>困难</t>
-  </si>
-  <si>
-    <t>雪山</t>
-  </si>
-  <si>
-    <t>很难</t>
-  </si>
-  <si>
-    <t>极难</t>
   </si>
 </sst>
 </file>
@@ -468,14 +453,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="5" width="13.25" customWidth="1"/>
+    <col min="3" max="8" width="13.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -491,27 +476,45 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -525,1405 +528,2314 @@
       <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B4" s="2">
         <v>10010</v>
       </c>
       <c r="C4" s="2">
         <v>3.12</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B5" s="2">
         <v>10020</v>
       </c>
       <c r="C5" s="2">
         <v>3.2</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B6" s="2">
         <v>10030</v>
       </c>
       <c r="C6" s="2">
         <v>3.36</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B7" s="2">
         <v>10040</v>
       </c>
       <c r="C7" s="2">
         <v>3.52</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B8" s="2">
         <v>10050</v>
       </c>
       <c r="C8" s="2">
         <v>3.6934999999999998</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B9" s="2">
         <v>10060</v>
       </c>
       <c r="C9" s="2">
         <v>3.8689</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D9" s="2">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B10" s="2">
         <v>10070</v>
       </c>
       <c r="C10" s="2">
         <v>4.0492999999999997</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D10" s="2">
+        <v>4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B11" s="2">
         <v>10080</v>
       </c>
       <c r="C11" s="2">
         <v>4.2213000000000003</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D11" s="2">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B12" s="2">
         <v>10090</v>
       </c>
       <c r="C12" s="2">
         <v>4.3935000000000004</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D12" s="2">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B13" s="2">
         <v>10100</v>
       </c>
       <c r="C13" s="2">
         <v>4.5682999999999998</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D13" s="2">
+        <v>5</v>
+      </c>
+      <c r="E13" s="2">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B14" s="2">
         <v>10110</v>
       </c>
       <c r="C14" s="2">
         <v>4.7430000000000003</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D14" s="2">
+        <v>6</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B15" s="2">
         <v>10120</v>
       </c>
       <c r="C15" s="2">
         <v>4.9172000000000002</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="D15" s="2">
+        <v>6</v>
+      </c>
+      <c r="E15" s="2">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B16" s="2">
         <v>10130</v>
       </c>
       <c r="C16" s="2">
         <v>5.0919999999999996</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D16" s="2">
+        <v>6</v>
+      </c>
+      <c r="E16" s="2">
+        <v>5</v>
+      </c>
+      <c r="F16" s="2">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="2">
         <v>10140</v>
       </c>
       <c r="C17" s="2">
         <v>5.2670000000000003</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D17" s="2">
+        <v>6</v>
+      </c>
+      <c r="E17" s="2">
+        <v>5</v>
+      </c>
+      <c r="F17" s="2">
+        <v>3</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="2">
         <v>10150</v>
       </c>
       <c r="C18" s="2">
         <v>5.4408000000000003</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D18" s="2">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2">
+        <v>5</v>
+      </c>
+      <c r="F18" s="2">
+        <v>4</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="2">
         <v>10160</v>
       </c>
       <c r="C19" s="2">
         <v>5.6146000000000003</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D19" s="2">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2">
+        <v>5</v>
+      </c>
+      <c r="F19" s="2">
+        <v>4</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="2">
         <v>10170</v>
       </c>
       <c r="C20" s="2">
         <v>5.7888000000000002</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D20" s="2">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2">
+        <v>4</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="2">
         <v>10180</v>
       </c>
       <c r="C21" s="2">
         <v>5.9637000000000002</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D21" s="2">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2">
+        <v>6</v>
+      </c>
+      <c r="F21" s="2">
+        <v>5</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="2">
         <v>10190</v>
       </c>
       <c r="C22" s="2">
         <v>6.1379000000000001</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D22" s="2">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2">
+        <v>6</v>
+      </c>
+      <c r="F22" s="2">
+        <v>5</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="2">
         <v>10200</v>
       </c>
       <c r="C23" s="2">
         <v>6.3125999999999998</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D23" s="2">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2">
+        <v>6</v>
+      </c>
+      <c r="F23" s="2">
+        <v>5</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="2">
         <v>10210</v>
       </c>
       <c r="C24" s="2">
         <v>6.4863999999999997</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D24" s="2">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2">
+        <v>7</v>
+      </c>
+      <c r="F24" s="2">
+        <v>5</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="2">
         <v>10220</v>
       </c>
       <c r="C25" s="2">
         <v>6.6604999999999999</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D25" s="2">
+        <v>9</v>
+      </c>
+      <c r="E25" s="2">
+        <v>7</v>
+      </c>
+      <c r="F25" s="2">
+        <v>6</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="2">
         <v>10230</v>
       </c>
       <c r="C26" s="2">
         <v>6.8349000000000002</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D26" s="2">
+        <v>9</v>
+      </c>
+      <c r="E26" s="2">
+        <v>7</v>
+      </c>
+      <c r="F26" s="2">
+        <v>6</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="2">
         <v>10240</v>
       </c>
       <c r="C27" s="2">
         <v>7.0083000000000002</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D27" s="2">
+        <v>9</v>
+      </c>
+      <c r="E27" s="2">
+        <v>7</v>
+      </c>
+      <c r="F27" s="2">
+        <v>6</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="2">
         <v>10250</v>
       </c>
       <c r="C28" s="2">
         <v>7.1832000000000003</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D28" s="2">
+        <v>9</v>
+      </c>
+      <c r="E28" s="2">
+        <v>8</v>
+      </c>
+      <c r="F28" s="2">
+        <v>6</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="2">
         <v>10260</v>
       </c>
       <c r="C29" s="2">
         <v>7.3582999999999998</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D29" s="2">
+        <v>9</v>
+      </c>
+      <c r="E29" s="2">
+        <v>8</v>
+      </c>
+      <c r="F29" s="2">
+        <v>6</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="2">
         <v>10270</v>
       </c>
       <c r="C30" s="2">
         <v>7.5328999999999997</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="2">
         <v>10</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="E30" s="2">
+        <v>8</v>
+      </c>
+      <c r="F30" s="2">
+        <v>7</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="2">
         <v>10280</v>
       </c>
       <c r="C31" s="2">
         <v>7.7065999999999999</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="2">
         <v>10</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="E31" s="2">
+        <v>8</v>
+      </c>
+      <c r="F31" s="2">
+        <v>7</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="2">
         <v>10290</v>
       </c>
       <c r="C32" s="2">
         <v>7.8804999999999996</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="2">
         <v>10</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="E32" s="2">
+        <v>8</v>
+      </c>
+      <c r="F32" s="2">
+        <v>7</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="2">
         <v>10300</v>
       </c>
       <c r="C33" s="2">
         <v>8.0551999999999992</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="2">
         <v>10</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="E33" s="2">
+        <v>9</v>
+      </c>
+      <c r="F33" s="2">
+        <v>7</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="2">
         <v>10310</v>
       </c>
       <c r="C34" s="2">
         <v>8.2296999999999993</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="2">
         <v>10</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="E34" s="2">
+        <v>9</v>
+      </c>
+      <c r="F34" s="2">
+        <v>7</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="2">
         <v>10320</v>
       </c>
       <c r="C35" s="2">
         <v>8.4039000000000001</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D35" s="2">
+        <v>11</v>
+      </c>
+      <c r="E35" s="2">
+        <v>9</v>
+      </c>
+      <c r="F35" s="2">
+        <v>8</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="2">
         <v>10330</v>
       </c>
       <c r="C36" s="2">
         <v>8.5782000000000007</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D36" s="2">
+        <v>11</v>
+      </c>
+      <c r="E36" s="2">
+        <v>9</v>
+      </c>
+      <c r="F36" s="2">
+        <v>8</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="2">
         <v>10340</v>
       </c>
       <c r="C37" s="2">
         <v>8.7528000000000006</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D37" s="2">
+        <v>11</v>
+      </c>
+      <c r="E37" s="2">
+        <v>9</v>
+      </c>
+      <c r="F37" s="2">
+        <v>8</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="2">
         <v>10350</v>
       </c>
       <c r="C38" s="2">
         <v>8.9265000000000008</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="2">
+        <v>11</v>
+      </c>
+      <c r="E38" s="2">
         <v>10</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="F38" s="2">
+        <v>8</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="2">
         <v>10360</v>
       </c>
       <c r="C39" s="2">
         <v>9.1013000000000002</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="2">
+        <v>11</v>
+      </c>
+      <c r="E39" s="2">
         <v>10</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="F39" s="2">
+        <v>8</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="2">
         <v>10370</v>
       </c>
       <c r="C40" s="2">
         <v>9.2753999999999994</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="2">
+        <v>11</v>
+      </c>
+      <c r="E40" s="2">
         <v>10</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="F40" s="2">
+        <v>8</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="2">
         <v>10380</v>
       </c>
       <c r="C41" s="2">
         <v>9.4495000000000005</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="2">
+        <v>12</v>
+      </c>
+      <c r="E41" s="2">
         <v>10</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="F41" s="2">
+        <v>9</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="2">
         <v>10390</v>
       </c>
       <c r="C42" s="2">
         <v>9.6242000000000001</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="2">
+        <v>12</v>
+      </c>
+      <c r="E42" s="2">
         <v>10</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="F42" s="2">
+        <v>9</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="2">
         <v>10400</v>
       </c>
       <c r="C43" s="2">
         <v>9.7982999999999993</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="2">
+        <v>12</v>
+      </c>
+      <c r="E43" s="2">
         <v>10</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="F43" s="2">
+        <v>9</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="2">
         <v>10410</v>
       </c>
       <c r="C44" s="2">
         <v>9.9724000000000004</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="2">
+        <v>12</v>
+      </c>
+      <c r="E44" s="2">
         <v>10</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="F44" s="2">
+        <v>9</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="2">
         <v>10420</v>
       </c>
       <c r="C45" s="2">
         <v>10.1469</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D45" s="2">
+        <v>12</v>
+      </c>
+      <c r="E45" s="2">
+        <v>11</v>
+      </c>
+      <c r="F45" s="2">
+        <v>9</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="2">
         <v>10430</v>
       </c>
       <c r="C46" s="2">
         <v>10.321099999999999</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D46" s="2">
+        <v>12</v>
+      </c>
+      <c r="E46" s="2">
+        <v>11</v>
+      </c>
+      <c r="F46" s="2">
+        <v>9</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B47" s="2">
         <v>10440</v>
       </c>
       <c r="C47" s="2">
         <v>10.495900000000001</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="2">
+        <v>13</v>
+      </c>
+      <c r="E47" s="2">
+        <v>11</v>
+      </c>
+      <c r="F47" s="2">
         <v>10</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="G47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B48" s="2">
         <v>10450</v>
       </c>
       <c r="C48" s="2">
         <v>10.669499999999999</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="2">
+        <v>13</v>
+      </c>
+      <c r="E48" s="2">
+        <v>11</v>
+      </c>
+      <c r="F48" s="2">
         <v>10</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="G48" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B49" s="2">
         <v>10460</v>
       </c>
       <c r="C49" s="2">
         <v>10.844200000000001</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="2">
+        <v>13</v>
+      </c>
+      <c r="E49" s="2">
+        <v>11</v>
+      </c>
+      <c r="F49" s="2">
         <v>10</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="G49" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B50" s="2">
         <v>10470</v>
       </c>
       <c r="C50" s="2">
         <v>11.0185</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="2">
+        <v>13</v>
+      </c>
+      <c r="E50" s="2">
+        <v>11</v>
+      </c>
+      <c r="F50" s="2">
         <v>10</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="G50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B51" s="2">
         <v>10480</v>
       </c>
       <c r="C51" s="2">
         <v>11.1927</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="2">
+        <v>13</v>
+      </c>
+      <c r="E51" s="2">
+        <v>12</v>
+      </c>
+      <c r="F51" s="2">
         <v>10</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="G51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B52" s="2">
         <v>10490</v>
       </c>
       <c r="C52" s="2">
         <v>11.367599999999999</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="2">
+        <v>13</v>
+      </c>
+      <c r="E52" s="2">
+        <v>12</v>
+      </c>
+      <c r="F52" s="2">
         <v>10</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="G52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B53" s="2">
         <v>10500</v>
       </c>
       <c r="C53" s="2">
         <v>11.541600000000001</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="2">
+        <v>13</v>
+      </c>
+      <c r="E53" s="2">
+        <v>12</v>
+      </c>
+      <c r="F53" s="2">
         <v>10</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="G53" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B54" s="2">
         <v>10510</v>
       </c>
       <c r="C54" s="2">
         <v>11.7158</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D54" s="2">
+        <v>14</v>
+      </c>
+      <c r="E54" s="2">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2">
+        <v>11</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B55" s="2">
         <v>10520</v>
       </c>
       <c r="C55" s="2">
         <v>11.889799999999999</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D55" s="2">
+        <v>14</v>
+      </c>
+      <c r="E55" s="2">
+        <v>12</v>
+      </c>
+      <c r="F55" s="2">
+        <v>11</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B56" s="2">
         <v>10530</v>
       </c>
       <c r="C56" s="2">
         <v>12.064500000000001</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D56" s="2">
+        <v>14</v>
+      </c>
+      <c r="E56" s="2">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2">
+        <v>11</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B57" s="2">
         <v>10540</v>
       </c>
       <c r="C57" s="2">
         <v>12.238799999999999</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D57" s="2">
+        <v>14</v>
+      </c>
+      <c r="E57" s="2">
+        <v>12</v>
+      </c>
+      <c r="F57" s="2">
+        <v>11</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B58" s="2">
         <v>10550</v>
       </c>
       <c r="C58" s="2">
         <v>12.4129</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D58" s="2">
+        <v>14</v>
+      </c>
+      <c r="E58" s="2">
+        <v>12</v>
+      </c>
+      <c r="F58" s="2">
+        <v>11</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B59" s="2">
         <v>10560</v>
       </c>
       <c r="C59" s="2">
         <v>12.5871</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D59" s="2">
+        <v>14</v>
+      </c>
+      <c r="E59" s="2">
+        <v>13</v>
+      </c>
+      <c r="F59" s="2">
+        <v>11</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B60" s="2">
         <v>10570</v>
       </c>
       <c r="C60" s="2">
         <v>12.760999999999999</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D60" s="2">
+        <v>14</v>
+      </c>
+      <c r="E60" s="2">
+        <v>13</v>
+      </c>
+      <c r="F60" s="2">
+        <v>11</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B61" s="2">
         <v>10580</v>
       </c>
       <c r="C61" s="2">
         <v>12.935700000000001</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D61" s="2">
+        <v>14</v>
+      </c>
+      <c r="E61" s="2">
+        <v>13</v>
+      </c>
+      <c r="F61" s="2">
+        <v>11</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B62" s="2">
         <v>10590</v>
       </c>
       <c r="C62" s="2">
         <v>13.110200000000001</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D62" s="2">
+        <v>15</v>
+      </c>
+      <c r="E62" s="2">
+        <v>13</v>
+      </c>
+      <c r="F62" s="2">
+        <v>12</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B63" s="2">
         <v>10600</v>
       </c>
       <c r="C63" s="2">
         <v>13.2845</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D63" s="2">
+        <v>15</v>
+      </c>
+      <c r="E63" s="2">
+        <v>13</v>
+      </c>
+      <c r="F63" s="2">
+        <v>12</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B64" s="2">
         <v>10610</v>
       </c>
       <c r="C64" s="2">
         <v>13.458399999999999</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D64" s="2">
+        <v>15</v>
+      </c>
+      <c r="E64" s="2">
+        <v>13</v>
+      </c>
+      <c r="F64" s="2">
+        <v>12</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B65" s="2">
         <v>10620</v>
       </c>
       <c r="C65" s="2">
         <v>13.6328</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D65" s="2">
+        <v>15</v>
+      </c>
+      <c r="E65" s="2">
+        <v>13</v>
+      </c>
+      <c r="F65" s="2">
+        <v>12</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B66" s="2">
         <v>10630</v>
       </c>
       <c r="C66" s="2">
         <v>13.807499999999999</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D66" s="2">
+        <v>15</v>
+      </c>
+      <c r="E66" s="2">
+        <v>13</v>
+      </c>
+      <c r="F66" s="2">
+        <v>12</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B67" s="2">
         <v>10640</v>
       </c>
       <c r="C67" s="2">
         <v>13.981999999999999</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D67" s="2">
+        <v>15</v>
+      </c>
+      <c r="E67" s="2">
+        <v>13</v>
+      </c>
+      <c r="F67" s="2">
+        <v>12</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B68" s="2">
         <v>10650</v>
       </c>
       <c r="C68" s="2">
         <v>14.156700000000001</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D68" s="2">
+        <v>15</v>
+      </c>
+      <c r="E68" s="2">
+        <v>14</v>
+      </c>
+      <c r="F68" s="2">
+        <v>12</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B69" s="2">
         <v>10660</v>
       </c>
       <c r="C69" s="2">
         <v>14.3307</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D69" s="2">
+        <v>15</v>
+      </c>
+      <c r="E69" s="2">
+        <v>14</v>
+      </c>
+      <c r="F69" s="2">
+        <v>12</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B70" s="2">
         <v>10670</v>
       </c>
       <c r="C70" s="2">
         <v>14.505100000000001</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D70" s="2">
+        <v>15</v>
+      </c>
+      <c r="E70" s="2">
+        <v>14</v>
+      </c>
+      <c r="F70" s="2">
+        <v>12</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B71" s="2">
         <v>10680</v>
       </c>
       <c r="C71" s="2">
         <v>14.6793</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D71" s="2">
+        <v>16</v>
+      </c>
+      <c r="E71" s="2">
+        <v>14</v>
+      </c>
+      <c r="F71" s="2">
+        <v>13</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B72" s="2">
         <v>10690</v>
       </c>
       <c r="C72" s="2">
         <v>14.853300000000001</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D72" s="2">
+        <v>16</v>
+      </c>
+      <c r="E72" s="2">
+        <v>14</v>
+      </c>
+      <c r="F72" s="2">
+        <v>13</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B73" s="2">
         <v>10700</v>
       </c>
       <c r="C73" s="2">
         <v>15.027900000000001</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D73" s="2">
+        <v>16</v>
+      </c>
+      <c r="E73" s="2">
+        <v>14</v>
+      </c>
+      <c r="F73" s="2">
+        <v>13</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B74" s="2">
         <v>10710</v>
       </c>
       <c r="C74" s="2">
         <v>15.202400000000001</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D74" s="2">
+        <v>16</v>
+      </c>
+      <c r="E74" s="2">
+        <v>14</v>
+      </c>
+      <c r="F74" s="2">
+        <v>13</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B75" s="2">
         <v>10720</v>
       </c>
       <c r="C75" s="2">
         <v>15.3766</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D75" s="2">
+        <v>16</v>
+      </c>
+      <c r="E75" s="2">
+        <v>14</v>
+      </c>
+      <c r="F75" s="2">
+        <v>13</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B76" s="2">
         <v>10730</v>
       </c>
       <c r="C76" s="2">
         <v>15.5504</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D76" s="2">
+        <v>16</v>
+      </c>
+      <c r="E76" s="2">
+        <v>14</v>
+      </c>
+      <c r="F76" s="2">
+        <v>13</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B77" s="2">
         <v>10740</v>
       </c>
       <c r="C77" s="2">
         <v>15.725</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D77" s="2">
+        <v>16</v>
+      </c>
+      <c r="E77" s="2">
+        <v>15</v>
+      </c>
+      <c r="F77" s="2">
+        <v>13</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B78" s="2">
         <v>10750</v>
       </c>
       <c r="C78" s="2">
         <v>15.8992</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D78" s="2">
+        <v>16</v>
+      </c>
+      <c r="E78" s="2">
+        <v>15</v>
+      </c>
+      <c r="F78" s="2">
+        <v>13</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B79" s="2">
         <v>10760</v>
       </c>
       <c r="C79" s="2">
         <v>16.0731</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D79" s="2">
+        <v>16</v>
+      </c>
+      <c r="E79" s="2">
+        <v>15</v>
+      </c>
+      <c r="F79" s="2">
+        <v>13</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B80" s="2">
         <v>10770</v>
       </c>
       <c r="C80" s="2">
         <v>16.247599999999998</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D80" s="2">
+        <v>16</v>
+      </c>
+      <c r="E80" s="2">
+        <v>15</v>
+      </c>
+      <c r="F80" s="2">
+        <v>13</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="2">
         <v>10780</v>
       </c>
       <c r="C81" s="2">
         <v>16.4224</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D81" s="2">
+        <v>17</v>
+      </c>
+      <c r="E81" s="2">
+        <v>15</v>
+      </c>
+      <c r="F81" s="2">
+        <v>14</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="2">
         <v>10790</v>
       </c>
       <c r="C82" s="2">
         <v>16.597000000000001</v>
       </c>
-      <c r="D82" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D82" s="2">
+        <v>17</v>
+      </c>
+      <c r="E82" s="2">
+        <v>15</v>
+      </c>
+      <c r="F82" s="2">
+        <v>14</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="2">
         <v>10800</v>
       </c>
       <c r="C83" s="2">
         <v>16.7715</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D83" s="2">
+        <v>17</v>
+      </c>
+      <c r="E83" s="2">
+        <v>15</v>
+      </c>
+      <c r="F83" s="2">
+        <v>14</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B84" s="2">
         <v>10810</v>
       </c>
       <c r="C84" s="2">
         <v>16.945799999999998</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D84" s="2">
+        <v>17</v>
+      </c>
+      <c r="E84" s="2">
+        <v>15</v>
+      </c>
+      <c r="F84" s="2">
+        <v>14</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="2">
         <v>10820</v>
       </c>
       <c r="C85" s="2">
         <v>17.119700000000002</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D85" s="2">
+        <v>17</v>
+      </c>
+      <c r="E85" s="2">
+        <v>15</v>
+      </c>
+      <c r="F85" s="2">
+        <v>14</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="2">
         <v>10830</v>
       </c>
       <c r="C86" s="2">
         <v>17.294</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D86" s="2">
+        <v>17</v>
+      </c>
+      <c r="E86" s="2">
+        <v>15</v>
+      </c>
+      <c r="F86" s="2">
+        <v>14</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="2">
         <v>10840</v>
       </c>
       <c r="C87" s="2">
         <v>17.468499999999999</v>
       </c>
-      <c r="D87" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D87" s="2">
+        <v>17</v>
+      </c>
+      <c r="E87" s="2">
+        <v>15</v>
+      </c>
+      <c r="F87" s="2">
+        <v>14</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="2">
         <v>10850</v>
       </c>
       <c r="C88" s="2">
         <v>17.6434</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D88" s="2">
+        <v>17</v>
+      </c>
+      <c r="E88" s="2">
+        <v>16</v>
+      </c>
+      <c r="F88" s="2">
+        <v>14</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="2">
         <v>10860</v>
       </c>
       <c r="C89" s="2">
         <v>17.8172</v>
       </c>
-      <c r="D89" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D89" s="2">
+        <v>17</v>
+      </c>
+      <c r="E89" s="2">
+        <v>16</v>
+      </c>
+      <c r="F89" s="2">
+        <v>14</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="2">
         <v>10870</v>
       </c>
       <c r="C90" s="2">
         <v>17.991499999999998</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D90" s="2">
+        <v>17</v>
+      </c>
+      <c r="E90" s="2">
+        <v>16</v>
+      </c>
+      <c r="F90" s="2">
+        <v>14</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="2">
         <v>10880</v>
       </c>
       <c r="C91" s="2">
         <v>18.165199999999999</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D91" s="2">
+        <v>17</v>
+      </c>
+      <c r="E91" s="2">
+        <v>16</v>
+      </c>
+      <c r="F91" s="2">
+        <v>14</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="2">
         <v>10890</v>
       </c>
       <c r="C92" s="2">
         <v>18.339400000000001</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D92" s="2">
+        <v>17</v>
+      </c>
+      <c r="E92" s="2">
+        <v>16</v>
+      </c>
+      <c r="F92" s="2">
+        <v>15</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="2">
         <v>10900</v>
       </c>
       <c r="C93" s="2">
         <v>18.513400000000001</v>
       </c>
-      <c r="D93" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D93" s="2">
+        <v>18</v>
+      </c>
+      <c r="E93" s="2">
+        <v>16</v>
+      </c>
+      <c r="F93" s="2">
+        <v>15</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B94" s="2">
         <v>10910</v>
       </c>
       <c r="C94" s="2">
         <v>18.688700000000001</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D94" s="2">
+        <v>18</v>
+      </c>
+      <c r="E94" s="2">
+        <v>16</v>
+      </c>
+      <c r="F94" s="2">
+        <v>15</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="2">
         <v>10920</v>
       </c>
       <c r="C95" s="2">
         <v>18.863099999999999</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D95" s="2">
+        <v>18</v>
+      </c>
+      <c r="E95" s="2">
+        <v>16</v>
+      </c>
+      <c r="F95" s="2">
+        <v>15</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="2">
         <v>10930</v>
       </c>
       <c r="C96" s="2">
         <v>19.036899999999999</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D96" s="2">
+        <v>18</v>
+      </c>
+      <c r="E96" s="2">
+        <v>16</v>
+      </c>
+      <c r="F96" s="2">
+        <v>15</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="2">
         <v>10940</v>
       </c>
       <c r="C97" s="2">
         <v>19.210699999999999</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D97" s="2">
+        <v>18</v>
+      </c>
+      <c r="E97" s="2">
+        <v>16</v>
+      </c>
+      <c r="F97" s="2">
+        <v>15</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="2">
         <v>10950</v>
       </c>
       <c r="C98" s="2">
         <v>19.385200000000001</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D98" s="2">
+        <v>18</v>
+      </c>
+      <c r="E98" s="2">
+        <v>16</v>
+      </c>
+      <c r="F98" s="2">
+        <v>15</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="2">
         <v>10960</v>
       </c>
       <c r="C99" s="2">
         <v>19.559899999999999</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D99" s="2">
+        <v>18</v>
+      </c>
+      <c r="E99" s="2">
+        <v>16</v>
+      </c>
+      <c r="F99" s="2">
+        <v>15</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="2">
         <v>10970</v>
       </c>
       <c r="C100" s="2">
         <v>19.733699999999999</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D100" s="2">
+        <v>18</v>
+      </c>
+      <c r="E100" s="2">
+        <v>17</v>
+      </c>
+      <c r="F100" s="2">
+        <v>15</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="2">
         <v>10980</v>
       </c>
       <c r="C101" s="2">
         <v>19.907800000000002</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D101" s="2">
+        <v>18</v>
+      </c>
+      <c r="E101" s="2">
+        <v>17</v>
+      </c>
+      <c r="F101" s="2">
+        <v>15</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="2">
         <v>10990</v>
       </c>
       <c r="C102" s="2">
         <v>20.0822</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.15">
+      <c r="D102" s="2">
+        <v>18</v>
+      </c>
+      <c r="E102" s="2">
+        <v>17</v>
+      </c>
+      <c r="F102" s="2">
+        <v>15</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="2">
         <v>11000</v>
       </c>
       <c r="C103" s="2">
         <v>20.198699999999999</v>
       </c>
-      <c r="D103" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>10</v>
+      <c r="D103" s="2">
+        <v>18</v>
+      </c>
+      <c r="E103" s="2">
+        <v>17</v>
+      </c>
+      <c r="F103" s="2">
+        <v>15</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/新数据生成/#关卡设计表_1导.xlsx
+++ b/新数据生成/#关卡设计表_1导.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -61,6 +61,24 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>简单</t>
+  </si>
+  <si>
+    <t>森林</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>困难</t>
+  </si>
+  <si>
+    <t>很难</t>
+  </si>
+  <si>
+    <t>极难</t>
   </si>
 </sst>
 </file>
@@ -555,10 +573,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
@@ -578,10 +596,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -601,10 +619,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.15">
@@ -624,10 +642,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
@@ -647,10 +665,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
@@ -670,10 +688,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -693,10 +711,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
@@ -716,10 +734,10 @@
         <v>2</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
@@ -739,10 +757,10 @@
         <v>2</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
@@ -762,10 +780,10 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
@@ -785,10 +803,10 @@
         <v>3</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">

--- a/新数据生成/#关卡设计表_1导.xlsx
+++ b/新数据生成/#关卡设计表_1导.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -41,13 +41,6 @@
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
@@ -105,14 +98,14 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
@@ -120,13 +113,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -509,2828 +499,2828 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>关卡编号</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>阵容强度</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>绿色等级</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>蓝色等级</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>紫色等级</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>关卡难度</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>适配地图</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>关卡编号</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>阵容强度</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>绿色等级</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>蓝色等级</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>紫色等级</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>关卡难度</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>适配地图</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="4" t="n">
         <v>10010</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="4" t="n">
         <v>3.2</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>10020</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="4" t="n">
         <v>3.64</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="4" t="n">
         <v>10030</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="4" t="n">
         <v>4.2736</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="4" t="n">
         <v>10040</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="4" t="n">
         <v>4.903</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="4" t="n">
         <v>10050</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="4" t="n">
         <v>5.5392</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="4" t="n">
         <v>10060</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="4" t="n">
         <v>6.1728</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="4" t="n">
         <v>10070</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="4" t="n">
         <v>6.8061</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="4" t="n">
         <v>10080</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4" t="n">
         <v>7.4424</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="4" t="n">
         <v>10090</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="4" t="n">
         <v>8.0687</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="4" t="n">
         <v>10100</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="4" t="n">
         <v>8.704800000000001</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="4" t="n">
         <v>10110</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="4" t="n">
         <v>9.343999999999999</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="4" t="n">
         <v>10120</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="4" t="n">
         <v>9.969900000000001</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="4" t="n">
         <v>10130</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="4" t="n">
         <v>10.6028</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="4" t="n">
         <v>10140</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="4" t="n">
         <v>11.2329</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="4" t="n">
         <v>10150</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="4" t="n">
         <v>11.8788</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="4" t="n">
         <v>10160</v>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="4" t="n">
         <v>12.5076</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="4" t="n">
         <v>10170</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="4" t="n">
         <v>13.1393</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="4" t="n">
         <v>10180</v>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="4" t="n">
         <v>13.7729</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="5" t="n">
+      <c r="B22" s="4" t="n">
         <v>10190</v>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="4" t="n">
         <v>14.4082</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="5" t="n">
+      <c r="B23" s="4" t="n">
         <v>10200</v>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="4" t="n">
         <v>15.0424</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="5" t="n">
+      <c r="B24" s="4" t="n">
         <v>10210</v>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="4" t="n">
         <v>15.676</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="5" t="n">
+      <c r="B25" s="4" t="n">
         <v>10220</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="4" t="n">
         <v>16.3105</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D25" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="5" t="n">
+      <c r="B26" s="4" t="n">
         <v>10230</v>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="4" t="n">
         <v>16.9422</v>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D26" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="5" t="n">
+      <c r="B27" s="4" t="n">
         <v>10240</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="4" t="n">
         <v>17.5779</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D27" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="5" t="n">
+      <c r="B28" s="4" t="n">
         <v>10250</v>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="4" t="n">
         <v>18.2134</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D28" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="5" t="n">
+      <c r="B29" s="4" t="n">
         <v>10260</v>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="4" t="n">
         <v>18.8451</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D29" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="5" t="n">
+      <c r="B30" s="4" t="n">
         <v>10270</v>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="4" t="n">
         <v>19.4834</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D30" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="5" t="n">
+      <c r="B31" s="4" t="n">
         <v>10280</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="4" t="n">
         <v>20.1143</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D31" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="5" t="n">
+      <c r="B32" s="4" t="n">
         <v>10290</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="4" t="n">
         <v>20.7479</v>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D32" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="4" t="n">
         <v>10300</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="4" t="n">
         <v>21.3829</v>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D33" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="5" t="n">
+      <c r="B34" s="4" t="n">
         <v>10310</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="4" t="n">
         <v>22.0169</v>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="5" t="n">
+      <c r="B35" s="4" t="n">
         <v>10320</v>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="4" t="n">
         <v>22.6537</v>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D35" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="5" t="n">
+      <c r="B36" s="4" t="n">
         <v>10330</v>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="4" t="n">
         <v>23.286</v>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D36" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="5" t="n">
+      <c r="B37" s="4" t="n">
         <v>10340</v>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="4" t="n">
         <v>23.9151</v>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="D37" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="5" t="n">
+      <c r="B38" s="4" t="n">
         <v>10350</v>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="4" t="n">
         <v>24.544</v>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D38" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="5" t="n">
+      <c r="B39" s="4" t="n">
         <v>10360</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="4" t="n">
         <v>25.1819</v>
       </c>
-      <c r="D39" s="5" t="n">
+      <c r="D39" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="5" t="n">
+      <c r="B40" s="4" t="n">
         <v>10370</v>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="4" t="n">
         <v>25.8207</v>
       </c>
-      <c r="D40" s="5" t="n">
+      <c r="D40" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="5" t="n">
+      <c r="B41" s="4" t="n">
         <v>10380</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="4" t="n">
         <v>26.4535</v>
       </c>
-      <c r="D41" s="5" t="n">
+      <c r="D41" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="5" t="n">
+      <c r="B42" s="4" t="n">
         <v>10390</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" s="4" t="n">
         <v>27.0849</v>
       </c>
-      <c r="D42" s="5" t="n">
+      <c r="D42" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="F42" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="5" t="n">
+      <c r="B43" s="4" t="n">
         <v>10400</v>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="4" t="n">
         <v>27.7189</v>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="D43" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="5" t="n">
+      <c r="B44" s="4" t="n">
         <v>10410</v>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="4" t="n">
         <v>28.3569</v>
       </c>
-      <c r="D44" s="5" t="n">
+      <c r="D44" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="F44" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="4" t="n">
         <v>10420</v>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="4" t="n">
         <v>28.9881</v>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D45" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="5" t="n">
+      <c r="B46" s="4" t="n">
         <v>10430</v>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" s="4" t="n">
         <v>29.6215</v>
       </c>
-      <c r="D46" s="5" t="n">
+      <c r="D46" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E46" s="5" t="n">
+      <c r="E46" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="5" t="n">
+      <c r="B47" s="4" t="n">
         <v>10440</v>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C47" s="4" t="n">
         <v>30.2499</v>
       </c>
-      <c r="D47" s="5" t="n">
+      <c r="D47" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E47" s="5" t="n">
+      <c r="E47" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="F47" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="5" t="n">
+      <c r="B48" s="4" t="n">
         <v>10450</v>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" s="4" t="n">
         <v>30.8882</v>
       </c>
-      <c r="D48" s="5" t="n">
+      <c r="D48" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="5" t="n">
+      <c r="E48" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F48" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="5" t="n">
+      <c r="B49" s="4" t="n">
         <v>10460</v>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C49" s="4" t="n">
         <v>31.5263</v>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D49" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="E49" s="5" t="n">
+      <c r="E49" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F49" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="5" t="n">
+      <c r="B50" s="4" t="n">
         <v>10470</v>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="4" t="n">
         <v>32.1574</v>
       </c>
-      <c r="D50" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E50" s="5" t="n">
+      <c r="D50" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F50" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="5" t="n">
+      <c r="B51" s="4" t="n">
         <v>10480</v>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="4" t="n">
         <v>32.7831</v>
       </c>
-      <c r="D51" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E51" s="5" t="n">
+      <c r="D51" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="F51" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G51" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="5" t="n">
+      <c r="B52" s="4" t="n">
         <v>10490</v>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C52" s="4" t="n">
         <v>33.4243</v>
       </c>
-      <c r="D52" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E52" s="5" t="n">
+      <c r="D52" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E52" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F52" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="5" t="n">
+      <c r="B53" s="4" t="n">
         <v>10500</v>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C53" s="4" t="n">
         <v>34.059</v>
       </c>
-      <c r="D53" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E53" s="5" t="n">
+      <c r="D53" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F53" s="5" t="n">
+      <c r="F53" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="5" t="n">
+      <c r="B54" s="4" t="n">
         <v>10510</v>
       </c>
-      <c r="C54" s="5" t="n">
+      <c r="C54" s="4" t="n">
         <v>34.6939</v>
       </c>
-      <c r="D54" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E54" s="5" t="n">
+      <c r="D54" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="F54" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="5" t="n">
+      <c r="B55" s="4" t="n">
         <v>10520</v>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C55" s="4" t="n">
         <v>35.3299</v>
       </c>
-      <c r="D55" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E55" s="5" t="n">
+      <c r="D55" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E55" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="F55" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="5" t="n">
+      <c r="B56" s="4" t="n">
         <v>10530</v>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="4" t="n">
         <v>35.9558</v>
       </c>
-      <c r="D56" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E56" s="5" t="n">
+      <c r="D56" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E56" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="F56" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="5" t="n">
+      <c r="B57" s="4" t="n">
         <v>10540</v>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C57" s="4" t="n">
         <v>36.5911</v>
       </c>
-      <c r="D57" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E57" s="5" t="n">
+      <c r="D57" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E57" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="F57" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="5" t="n">
+      <c r="B58" s="4" t="n">
         <v>10550</v>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" s="4" t="n">
         <v>37.2203</v>
       </c>
-      <c r="D58" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E58" s="5" t="n">
+      <c r="D58" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F58" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="G58" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="5" t="n">
+      <c r="B59" s="4" t="n">
         <v>10560</v>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C59" s="4" t="n">
         <v>37.8633</v>
       </c>
-      <c r="D59" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E59" s="5" t="n">
+      <c r="D59" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E59" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F59" s="5" t="n">
+      <c r="F59" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G59" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="5" t="n">
+      <c r="B60" s="4" t="n">
         <v>10570</v>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C60" s="4" t="n">
         <v>38.4962</v>
       </c>
-      <c r="D60" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E60" s="5" t="n">
+      <c r="D60" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="F60" s="5" t="n">
+      <c r="F60" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G60" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="5" t="n">
+      <c r="B61" s="4" t="n">
         <v>10580</v>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C61" s="4" t="n">
         <v>39.1272</v>
       </c>
-      <c r="D61" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F61" s="5" t="n">
+      <c r="D61" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F61" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G61" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="5" t="n">
+      <c r="B62" s="4" t="n">
         <v>10590</v>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C62" s="4" t="n">
         <v>39.7663</v>
       </c>
-      <c r="D62" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F62" s="5" t="n">
+      <c r="D62" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F62" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G62" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="5" t="n">
+      <c r="B63" s="4" t="n">
         <v>10600</v>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C63" s="4" t="n">
         <v>40.3927</v>
       </c>
-      <c r="D63" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F63" s="5" t="n">
+      <c r="D63" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F63" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G63" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="5" t="n">
+      <c r="B64" s="4" t="n">
         <v>10610</v>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C64" s="4" t="n">
         <v>41.0263</v>
       </c>
-      <c r="D64" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F64" s="5" t="n">
+      <c r="D64" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F64" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="5" t="n">
+      <c r="B65" s="4" t="n">
         <v>10620</v>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C65" s="4" t="n">
         <v>41.66</v>
       </c>
-      <c r="D65" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F65" s="5" t="n">
+      <c r="D65" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F65" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G65" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="5" t="n">
+      <c r="B66" s="4" t="n">
         <v>10630</v>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C66" s="4" t="n">
         <v>42.2958</v>
       </c>
-      <c r="D66" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F66" s="5" t="n">
+      <c r="D66" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F66" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G66" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="5" t="n">
+      <c r="B67" s="4" t="n">
         <v>10640</v>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C67" s="4" t="n">
         <v>42.9294</v>
       </c>
-      <c r="D67" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F67" s="5" t="n">
+      <c r="D67" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F67" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G67" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="5" t="n">
+      <c r="B68" s="4" t="n">
         <v>10650</v>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C68" s="4" t="n">
         <v>43.5598</v>
       </c>
-      <c r="D68" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F68" s="5" t="n">
+      <c r="D68" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F68" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G68" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="5" t="n">
+      <c r="B69" s="4" t="n">
         <v>10660</v>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C69" s="4" t="n">
         <v>44.1996</v>
       </c>
-      <c r="D69" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F69" s="5" t="n">
+      <c r="D69" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F69" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="5" t="n">
+      <c r="B70" s="4" t="n">
         <v>10670</v>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C70" s="4" t="n">
         <v>44.8384</v>
       </c>
-      <c r="D70" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F70" s="5" t="n">
+      <c r="D70" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F70" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="G70" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="5" t="n">
+      <c r="B71" s="4" t="n">
         <v>10680</v>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C71" s="4" t="n">
         <v>45.465</v>
       </c>
-      <c r="D71" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="D71" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="5" t="n">
+      <c r="B72" s="4" t="n">
         <v>10690</v>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C72" s="4" t="n">
         <v>46.1002</v>
       </c>
-      <c r="D72" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G72" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="D72" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="5" t="n">
+      <c r="B73" s="4" t="n">
         <v>10700</v>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C73" s="4" t="n">
         <v>46.7346</v>
       </c>
-      <c r="D73" s="5" t="n">
+      <c r="D73" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E73" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E73" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="5" t="n">
+      <c r="B74" s="4" t="n">
         <v>10710</v>
       </c>
-      <c r="C74" s="5" t="n">
+      <c r="C74" s="4" t="n">
         <v>47.3672</v>
       </c>
-      <c r="D74" s="5" t="n">
+      <c r="D74" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E74" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G74" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E74" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="5" t="n">
+      <c r="B75" s="4" t="n">
         <v>10720</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C75" s="4" t="n">
         <v>48.0008</v>
       </c>
-      <c r="D75" s="5" t="n">
+      <c r="D75" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E75" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G75" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E75" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="5" t="n">
+      <c r="B76" s="4" t="n">
         <v>10730</v>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C76" s="4" t="n">
         <v>48.6302</v>
       </c>
-      <c r="D76" s="5" t="n">
+      <c r="D76" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E76" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G76" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E76" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="5" t="n">
+      <c r="B77" s="4" t="n">
         <v>10740</v>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C77" s="4" t="n">
         <v>49.2697</v>
       </c>
-      <c r="D77" s="5" t="n">
+      <c r="D77" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E77" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G77" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E77" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="5" t="n">
+      <c r="B78" s="4" t="n">
         <v>10750</v>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C78" s="4" t="n">
         <v>49.9076</v>
       </c>
-      <c r="D78" s="5" t="n">
+      <c r="D78" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E78" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G78" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E78" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="5" t="n">
+      <c r="B79" s="4" t="n">
         <v>10760</v>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C79" s="4" t="n">
         <v>50.5374</v>
       </c>
-      <c r="D79" s="5" t="n">
+      <c r="D79" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E79" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E79" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="5" t="n">
+      <c r="B80" s="4" t="n">
         <v>10770</v>
       </c>
-      <c r="C80" s="5" t="n">
+      <c r="C80" s="4" t="n">
         <v>51.1791</v>
       </c>
-      <c r="D80" s="5" t="n">
+      <c r="D80" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E80" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E80" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="5" t="n">
+      <c r="B81" s="4" t="n">
         <v>10780</v>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C81" s="4" t="n">
         <v>51.8023</v>
       </c>
-      <c r="D81" s="5" t="n">
+      <c r="D81" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E81" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G81" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E81" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="5" t="n">
+      <c r="B82" s="4" t="n">
         <v>10790</v>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C82" s="4" t="n">
         <v>52.4325</v>
       </c>
-      <c r="D82" s="5" t="n">
+      <c r="D82" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E82" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E82" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="5" t="n">
+      <c r="B83" s="4" t="n">
         <v>10800</v>
       </c>
-      <c r="C83" s="5" t="n">
+      <c r="C83" s="4" t="n">
         <v>53.0864</v>
       </c>
-      <c r="D83" s="5" t="n">
+      <c r="D83" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E83" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G83" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E83" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="5" t="n">
+      <c r="B84" s="4" t="n">
         <v>10810</v>
       </c>
-      <c r="C84" s="5" t="n">
+      <c r="C84" s="4" t="n">
         <v>53.7071</v>
       </c>
-      <c r="D84" s="5" t="n">
+      <c r="D84" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E84" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E84" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="5" t="n">
+      <c r="B85" s="4" t="n">
         <v>10820</v>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C85" s="4" t="n">
         <v>54.3301</v>
       </c>
-      <c r="D85" s="5" t="n">
+      <c r="D85" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E85" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G85" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E85" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="5" t="n">
+      <c r="B86" s="4" t="n">
         <v>10830</v>
       </c>
-      <c r="C86" s="5" t="n">
+      <c r="C86" s="4" t="n">
         <v>54.9747</v>
       </c>
-      <c r="D86" s="5" t="n">
+      <c r="D86" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="E86" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="E86" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="5" t="n">
+      <c r="B87" s="4" t="n">
         <v>10840</v>
       </c>
-      <c r="C87" s="5" t="n">
+      <c r="C87" s="4" t="n">
         <v>55.6164</v>
       </c>
-      <c r="D87" s="5" t="n">
+      <c r="D87" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E87" s="5" t="n">
+      <c r="E87" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F87" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F87" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>极难</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="5" t="n">
+      <c r="B88" s="4" t="n">
         <v>10850</v>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C88" s="4" t="n">
         <v>56.2475</v>
       </c>
-      <c r="D88" s="5" t="n">
+      <c r="D88" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E88" s="5" t="n">
+      <c r="E88" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F88" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F88" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="5" t="n">
+      <c r="B89" s="4" t="n">
         <v>10860</v>
       </c>
-      <c r="C89" s="5" t="n">
+      <c r="C89" s="4" t="n">
         <v>56.8793</v>
       </c>
-      <c r="D89" s="5" t="n">
+      <c r="D89" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E89" s="5" t="n">
+      <c r="E89" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H89" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F89" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="5" t="n">
+      <c r="B90" s="4" t="n">
         <v>10870</v>
       </c>
-      <c r="C90" s="5" t="n">
+      <c r="C90" s="4" t="n">
         <v>57.5125</v>
       </c>
-      <c r="D90" s="5" t="n">
+      <c r="D90" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E90" s="5" t="n">
+      <c r="E90" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F90" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G90" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F90" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="5" t="n">
+      <c r="B91" s="4" t="n">
         <v>10880</v>
       </c>
-      <c r="C91" s="5" t="n">
+      <c r="C91" s="4" t="n">
         <v>58.1444</v>
       </c>
-      <c r="D91" s="5" t="n">
+      <c r="D91" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E91" s="5" t="n">
+      <c r="E91" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F91" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="5" t="n">
+      <c r="B92" s="4" t="n">
         <v>10890</v>
       </c>
-      <c r="C92" s="5" t="n">
+      <c r="C92" s="4" t="n">
         <v>58.7803</v>
       </c>
-      <c r="D92" s="5" t="n">
+      <c r="D92" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E92" s="5" t="n">
+      <c r="E92" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G92" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F92" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="5" t="n">
+      <c r="B93" s="4" t="n">
         <v>10900</v>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C93" s="4" t="n">
         <v>59.4119</v>
       </c>
-      <c r="D93" s="5" t="n">
+      <c r="D93" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E93" s="5" t="n">
+      <c r="E93" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F93" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="5" t="n">
+      <c r="B94" s="4" t="n">
         <v>10910</v>
       </c>
-      <c r="C94" s="5" t="n">
+      <c r="C94" s="4" t="n">
         <v>60.0425</v>
       </c>
-      <c r="D94" s="5" t="n">
+      <c r="D94" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E94" s="5" t="n">
+      <c r="E94" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F94" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="5" t="n">
+      <c r="B95" s="4" t="n">
         <v>10920</v>
       </c>
-      <c r="C95" s="5" t="n">
+      <c r="C95" s="4" t="n">
         <v>60.6768</v>
       </c>
-      <c r="D95" s="5" t="n">
+      <c r="D95" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E95" s="5" t="n">
+      <c r="E95" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F95" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F95" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>Desert</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="5" t="n">
+      <c r="B96" s="4" t="n">
         <v>10930</v>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C96" s="4" t="n">
         <v>61.3154</v>
       </c>
-      <c r="D96" s="5" t="n">
+      <c r="D96" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E96" s="5" t="n">
+      <c r="E96" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F96" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G96" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H96" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F96" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Winter</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="5" t="n">
+      <c r="B97" s="4" t="n">
         <v>10940</v>
       </c>
-      <c r="C97" s="5" t="n">
+      <c r="C97" s="4" t="n">
         <v>61.9471</v>
       </c>
-      <c r="D97" s="5" t="n">
+      <c r="D97" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E97" s="5" t="n">
+      <c r="E97" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F97" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H97" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F97" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>很难</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Lava</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="5" t="n">
+      <c r="B98" s="4" t="n">
         <v>10950</v>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="C98" s="4" t="n">
         <v>62.5828</v>
       </c>
-      <c r="D98" s="5" t="n">
+      <c r="D98" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E98" s="5" t="n">
+      <c r="E98" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G98" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H98" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F98" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="5" t="n">
+      <c r="B99" s="4" t="n">
         <v>10960</v>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C99" s="4" t="n">
         <v>63.2065</v>
       </c>
-      <c r="D99" s="5" t="n">
+      <c r="D99" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E99" s="5" t="n">
+      <c r="E99" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F99" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F99" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="5" t="n">
+      <c r="B100" s="4" t="n">
         <v>10970</v>
       </c>
-      <c r="C100" s="5" t="n">
+      <c r="C100" s="4" t="n">
         <v>63.8491</v>
       </c>
-      <c r="D100" s="5" t="n">
+      <c r="D100" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E100" s="5" t="n">
+      <c r="E100" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F100" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G100" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H100" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F100" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>Forest</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="5" t="n">
+      <c r="B101" s="4" t="n">
         <v>10980</v>
       </c>
-      <c r="C101" s="5" t="n">
+      <c r="C101" s="4" t="n">
         <v>64.4752</v>
       </c>
-      <c r="D101" s="5" t="n">
+      <c r="D101" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E101" s="5" t="n">
+      <c r="E101" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F101" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H101" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="F101" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="5" t="n">
+      <c r="B102" s="4" t="n">
         <v>10990</v>
       </c>
-      <c r="C102" s="5" t="n">
+      <c r="C102" s="4" t="n">
         <v>65.1129</v>
       </c>
-      <c r="D102" s="5" t="n">
+      <c r="D102" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E102" s="5" t="n">
+      <c r="E102" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F102" s="5" t="n">
+      <c r="F102" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G102" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>Darkland</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="5" t="n">
+      <c r="B103" s="4" t="n">
         <v>11000</v>
       </c>
-      <c r="C103" s="5" t="n">
+      <c r="C103" s="4" t="n">
         <v>65.5314</v>
       </c>
-      <c r="D103" s="5" t="n">
+      <c r="D103" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="E103" s="5" t="n">
+      <c r="E103" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="F103" s="5" t="n">
+      <c r="F103" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="G103" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>简单</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>Skyland</t>
         </is>
       </c>
     </row>
